--- a/scripts/templates/settings-onboarding-template.xlsx
+++ b/scripts/templates/settings-onboarding-template.xlsx
@@ -3,15 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="academic_years" sheetId="1" r:id="rId1"/>
-    <sheet name="subjects" sheetId="2" r:id="rId2"/>
-    <sheet name="classes" sheetId="3" r:id="rId3"/>
-    <sheet name="sections" sheetId="4" r:id="rId4"/>
-    <sheet name="levels" sheetId="5" r:id="rId5"/>
-    <sheet name="assessment_types" sheetId="6" r:id="rId6"/>
-    <sheet name="leave_quota" sheetId="7" r:id="rId7"/>
-    <sheet name="library_categories" sheetId="8" r:id="rId8"/>
-    <sheet name="inventory_categories" sheetId="9" r:id="rId9"/>
+    <sheet name="subjects" sheetId="1" r:id="rId1"/>
+    <sheet name="classes" sheetId="2" r:id="rId2"/>
+    <sheet name="levels" sheetId="3" r:id="rId3"/>
+    <sheet name="assessment_types" sheetId="4" r:id="rId4"/>
+    <sheet name="subject_templates" sheetId="5" r:id="rId5"/>
+    <sheet name="school_days" sheetId="6" r:id="rId6"/>
+    <sheet name="timing_templates" sheetId="7" r:id="rId7"/>
+    <sheet name="timing_slots" sheetId="8" r:id="rId8"/>
+    <sheet name="grade_templates" sheetId="9" r:id="rId9"/>
+    <sheet name="grade_ranges" sheetId="10" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
@@ -405,77 +406,559 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:C4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>name</v>
       </c>
       <c r="B1" t="str">
-        <v>start_date</v>
+        <v>code</v>
       </c>
       <c r="C1" t="str">
-        <v>end_date</v>
-      </c>
-      <c r="D1" t="str">
-        <v>set_active</v>
+        <v>lang_code</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-2027</v>
+        <v>Mathematics</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-09-01</v>
+        <v>MATH</v>
       </c>
       <c r="C2" t="str">
-        <v>2027-06-30</v>
-      </c>
-      <c r="D2" t="str">
-        <v>true</v>
+        <v>EN</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>رياضيات</v>
+      </c>
+      <c r="B3" t="str">
+        <v>MATH</v>
+      </c>
+      <c r="C3" t="str">
+        <v>AR</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>English</v>
+      </c>
+      <c r="B4" t="str">
+        <v>ENG</v>
+      </c>
+      <c r="C4" t="str">
+        <v>EN</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>name_en</v>
+        <v>template_name</v>
       </c>
       <c r="B1" t="str">
-        <v>name_ar</v>
+        <v>letter</v>
       </c>
       <c r="C1" t="str">
-        <v>code</v>
+        <v>min_percentage</v>
+      </c>
+      <c r="D1" t="str">
+        <v>max_percentage</v>
+      </c>
+      <c r="E1" t="str">
+        <v>sort_order</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Mathematics</v>
+        <v>Primary Grades</v>
       </c>
       <c r="B2" t="str">
-        <v>رياضيات</v>
+        <v>A</v>
       </c>
       <c r="C2" t="str">
-        <v>MATH</v>
+        <v>80</v>
+      </c>
+      <c r="D2" t="str">
+        <v>100</v>
+      </c>
+      <c r="E2" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Primary Grades</v>
+      </c>
+      <c r="B3" t="str">
+        <v>B</v>
+      </c>
+      <c r="C3" t="str">
+        <v>65</v>
+      </c>
+      <c r="D3" t="str">
+        <v>79</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Primary Grades</v>
+      </c>
+      <c r="B4" t="str">
+        <v>C</v>
+      </c>
+      <c r="C4" t="str">
+        <v>50</v>
+      </c>
+      <c r="D4" t="str">
+        <v>64</v>
+      </c>
+      <c r="E4" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Primary Grades</v>
+      </c>
+      <c r="B5" t="str">
+        <v>D</v>
+      </c>
+      <c r="C5" t="str">
+        <v>40</v>
+      </c>
+      <c r="D5" t="str">
+        <v>49</v>
+      </c>
+      <c r="E5" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Primary Grades</v>
+      </c>
+      <c r="B6" t="str">
+        <v>F</v>
+      </c>
+      <c r="C6" t="str">
+        <v>0</v>
+      </c>
+      <c r="D6" t="str">
+        <v>39</v>
+      </c>
+      <c r="E6" t="str">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>display_name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>sort_order</v>
+      </c>
+      <c r="D1" t="str">
+        <v>section_names</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Grade 1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Grade 1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>1</v>
+      </c>
+      <c r="D2" t="str">
+        <v>A,B</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Grade 2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Grade 2</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2</v>
+      </c>
+      <c r="D3" t="str">
+        <v>A,B</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>class_names</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Grade 1,Grade 2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>code</v>
+      </c>
+      <c r="C1" t="str">
+        <v>lang_code</v>
+      </c>
+      <c r="D1" t="str">
+        <v>sort_order</v>
+      </c>
+      <c r="E1" t="str">
+        <v>is_term_examination</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Mid Term</v>
+      </c>
+      <c r="B2" t="str">
+        <v>MID</v>
+      </c>
+      <c r="C2" t="str">
+        <v>EN</v>
+      </c>
+      <c r="D2" t="str">
+        <v>1</v>
+      </c>
+      <c r="E2" t="str">
+        <v>yes</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Final</v>
+      </c>
+      <c r="B3" t="str">
+        <v>FINAL</v>
+      </c>
+      <c r="C3" t="str">
+        <v>EN</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2</v>
+      </c>
+      <c r="E3" t="str">
+        <v>yes</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Quiz</v>
+      </c>
+      <c r="B4" t="str">
+        <v>QUIZ</v>
+      </c>
+      <c r="C4" t="str">
+        <v>EN</v>
+      </c>
+      <c r="D4" t="str">
+        <v>3</v>
+      </c>
+      <c r="E4" t="str">
+        <v>no</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>description</v>
+      </c>
+      <c r="C1" t="str">
+        <v>subject_names</v>
+      </c>
+      <c r="D1" t="str">
+        <v>assign_mode</v>
+      </c>
+      <c r="E1" t="str">
+        <v>assign_names</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Primary Core</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Core subjects for primary classes</v>
+      </c>
+      <c r="C2" t="str">
+        <v>MATH,ENG</v>
+      </c>
+      <c r="D2" t="str">
+        <v>classes</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Grade 1,Grade 2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B8"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>day</v>
+      </c>
+      <c r="B1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Sunday</v>
+      </c>
+      <c r="B2" t="str">
+        <v>N</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Tuesday</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Wednesday</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Thursday</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="B8" t="str">
+        <v>N</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>start_time</v>
+      </c>
+      <c r="C1" t="str">
+        <v>end_time</v>
+      </c>
+      <c r="D1" t="str">
+        <v>period_duration_minutes</v>
+      </c>
+      <c r="E1" t="str">
+        <v>assigned_class_names</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Primary Day</v>
+      </c>
+      <c r="B2" t="str">
+        <v>07:30</v>
+      </c>
+      <c r="C2" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="D2" t="str">
+        <v>40</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Grade 1,Grade 2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>template_name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>slot_name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>start_time</v>
+      </c>
+      <c r="D1" t="str">
+        <v>end_time</v>
+      </c>
+      <c r="E1" t="str">
+        <v>sort_order</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Primary Day</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Break</v>
+      </c>
+      <c r="C2" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="D2" t="str">
+        <v>10:20</v>
+      </c>
+      <c r="E2" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Primary Day</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Lunch</v>
+      </c>
+      <c r="C3" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="D3" t="str">
+        <v>12:40</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
   <sheetData>
@@ -484,21 +967,21 @@
         <v>name</v>
       </c>
       <c r="B1" t="str">
-        <v>display_name</v>
+        <v>assigned_class_names</v>
       </c>
       <c r="C1" t="str">
-        <v>sort_order</v>
+        <v>minimum_passing_grade</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Grade 1</v>
+        <v>Primary Grades</v>
       </c>
       <c r="B2" t="str">
-        <v>Grade 1</v>
+        <v>Grade 1,Grade 2</v>
       </c>
       <c r="C2" t="str">
-        <v>1</v>
+        <v>D</v>
       </c>
     </row>
   </sheetData>
@@ -506,154 +989,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>sort_order</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>A</v>
-      </c>
-      <c r="B2" t="str">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>class_names</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Primary</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Grade 1,Grade 2,Grade 3</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>name_en</v>
-      </c>
-      <c r="B1" t="str">
-        <v>name_ar</v>
-      </c>
-      <c r="C1" t="str">
-        <v>sort_order</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Quiz</v>
-      </c>
-      <c r="B2" t="str">
-        <v>اختبار قصير</v>
-      </c>
-      <c r="C2" t="str">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>annual_quota</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>category</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>General Knowledge</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>category</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Uniforms</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
-  </ignoredErrors>
-</worksheet>
 </file>